--- a/Vulnerability_Test_Cases_100.xlsx
+++ b/Vulnerability_Test_Cases_100.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 09:23:37</t>
+          <t>2026-06-22 10:04:40</t>
         </is>
       </c>
     </row>
